--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -54469,13 +54469,13 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O300" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R300" t="n">
-        <v>0.06589097740892956</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
@@ -54575,12 +54575,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -54605,7 +54605,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -54614,81 +54614,95 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O301" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R301" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.05606928256970008</v>
       </c>
       <c r="S301" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR301" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS301" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ301" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS301" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54715,17 +54729,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -54750,7 +54764,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -54759,26 +54773,103 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O302" t="n">
-        <v>0</v>
-      </c>
-      <c r="P302" t="n">
-        <v>0</v>
-      </c>
-      <c r="R302" t="n">
-        <v>0</v>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>6</v>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>Hepatit E</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ302" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK302" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM302" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN302" t="b">
+        <v>1</v>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
@@ -54787,7 +54878,7 @@
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ302" t="inlineStr">
@@ -54797,55 +54888,55 @@
       </c>
       <c r="AS302" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT302" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54872,17 +54963,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -54916,173 +55007,81 @@
         </is>
       </c>
       <c r="N303" t="n">
+        <v>13</v>
+      </c>
+      <c r="O303" t="n">
+        <v>13</v>
+      </c>
+      <c r="R303" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO303" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP303" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR303" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS303" t="inlineStr"/>
+      <c r="AT303" t="n">
         <v>0</v>
       </c>
-      <c r="O303" t="n">
-        <v>0</v>
-      </c>
-      <c r="P303" t="n">
-        <v>0</v>
-      </c>
-      <c r="U303" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V303" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W303" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X303" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y303" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z303" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA303" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB303" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC303" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD303" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE303" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF303" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG303" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH303" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI303" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ303" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK303" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM303" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN303" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO303" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP303" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ303" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS303" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT303" t="n">
-        <v>2</v>
-      </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55114,12 +55113,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -55144,7 +55143,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -55153,81 +55152,93 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O304" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="P304" t="n">
+        <v>0</v>
       </c>
       <c r="R304" t="n">
-        <v>0.007351275668091897</v>
+        <v>0</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR304" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS304" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ304" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS304" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT304" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -55254,7 +55265,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -55289,7 +55300,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -55298,26 +55309,106 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O305" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P305" t="n">
-        <v>3</v>
-      </c>
-      <c r="R305" t="n">
-        <v>0.05079797265291142</v>
-      </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ305" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK305" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM305" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN305" t="b">
+        <v>1</v>
       </c>
       <c r="AO305" t="inlineStr">
         <is>
@@ -55411,17 +55502,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -55455,173 +55546,81 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O306" t="n">
-        <v>3</v>
-      </c>
-      <c r="P306" t="n">
-        <v>3</v>
-      </c>
-      <c r="U306" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V306" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W306" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X306" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y306" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z306" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA306" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB306" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC306" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD306" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE306" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF306" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG306" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH306" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI306" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ306" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK306" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM306" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN306" t="b">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="R306" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO306" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP306" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ306" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS306" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR306" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS306" t="inlineStr"/>
       <c r="AT306" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV306" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55653,12 +55652,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -55683,7 +55682,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -55692,81 +55691,93 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O307" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="P307" t="n">
+        <v>3</v>
       </c>
       <c r="R307" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.05079797265291142</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP307" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR307" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS307" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ307" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS307" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV307" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA307" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB307" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC307" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -55793,7 +55804,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -55828,7 +55839,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -55837,26 +55848,106 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O308" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P308" t="n">
-        <v>0</v>
-      </c>
-      <c r="R308" t="n">
-        <v>0</v>
-      </c>
-      <c r="S308" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB308" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC308" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF308" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG308" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH308" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI308" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ308" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK308" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM308" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN308" t="b">
+        <v>1</v>
       </c>
       <c r="AO308" t="inlineStr">
         <is>
@@ -55950,17 +56041,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -55994,173 +56085,81 @@
         </is>
       </c>
       <c r="N309" t="n">
+        <v>8</v>
+      </c>
+      <c r="O309" t="n">
+        <v>8</v>
+      </c>
+      <c r="R309" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO309" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP309" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR309" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS309" t="inlineStr"/>
+      <c r="AT309" t="n">
         <v>0</v>
       </c>
-      <c r="O309" t="n">
-        <v>0</v>
-      </c>
-      <c r="P309" t="n">
-        <v>0</v>
-      </c>
-      <c r="U309" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V309" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W309" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X309" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y309" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z309" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA309" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB309" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC309" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD309" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE309" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF309" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG309" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH309" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI309" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ309" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK309" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM309" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN309" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO309" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP309" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ309" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS309" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT309" t="n">
-        <v>2</v>
-      </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56192,12 +56191,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -56222,7 +56221,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -56231,81 +56230,93 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O310" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="P310" t="n">
+        <v>0</v>
       </c>
       <c r="R310" t="n">
-        <v>0.004900850445394598</v>
+        <v>0</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP310" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR310" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS310" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ310" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS310" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT310" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV310" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA310" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB310" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC310" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56332,7 +56343,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -56367,7 +56378,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -56376,26 +56387,106 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O311" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P311" t="n">
-        <v>4</v>
-      </c>
-      <c r="R311" t="n">
-        <v>0.0677306302038819</v>
-      </c>
-      <c r="S311" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ311" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK311" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM311" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN311" t="b">
+        <v>1</v>
       </c>
       <c r="AO311" t="inlineStr">
         <is>
@@ -56489,17 +56580,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -56533,173 +56624,81 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O312" t="n">
-        <v>4</v>
-      </c>
-      <c r="P312" t="n">
-        <v>4</v>
-      </c>
-      <c r="U312" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V312" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W312" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X312" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y312" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z312" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA312" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB312" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC312" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD312" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE312" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF312" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG312" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH312" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI312" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ312" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK312" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM312" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN312" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R312" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO312" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP312" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ312" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS312" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR312" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr"/>
       <c r="AT312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56731,12 +56730,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -56761,90 +56760,102 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N313" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O313" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P313" t="n">
+        <v>4</v>
       </c>
       <c r="R313" t="n">
-        <v>0</v>
+        <v>0.0677306302038819</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP313" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR313" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS313" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ313" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV313" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA313" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB313" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC313" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56871,17 +56882,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -56906,104 +56917,182 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N314" t="n">
+        <v>4</v>
+      </c>
+      <c r="O314" t="n">
+        <v>4</v>
+      </c>
+      <c r="P314" t="n">
+        <v>4</v>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ314" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK314" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM314" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN314" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP314" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT314" t="n">
         <v>2</v>
       </c>
-      <c r="O314" t="n">
-        <v>2</v>
-      </c>
-      <c r="R314" t="n">
-        <v>0.03557618341728275</v>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AA314" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO314" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP314" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ314" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS314" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AT314" t="n">
-        <v>1</v>
-      </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV314" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA314" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57030,17 +57119,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -57074,170 +57163,81 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O315" t="n">
-        <v>2</v>
-      </c>
-      <c r="U315" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W315" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X315" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA315" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC315" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD315" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R315" t="n">
+        <v>0</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr"/>
+      <c r="AT315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV315" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE315" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG315" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK315" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM315" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN315" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO315" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP315" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ315" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS315" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AT315" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU315" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV315" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -57269,12 +57269,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -57314,73 +57314,466 @@
         <v>2</v>
       </c>
       <c r="R316" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV316" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW316" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA316" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>2</v>
+      </c>
+      <c r="O317" t="n">
+        <v>2</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN317" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>7</v>
+      </c>
+      <c r="O318" t="n">
+        <v>7</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0.01356578946654432</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP316" t="inlineStr">
+      <c r="AP318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR316" t="inlineStr">
+      <c r="AR318" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS316" t="inlineStr"/>
-      <c r="AT316" t="n">
+      <c r="AS318" t="inlineStr"/>
+      <c r="AT318" t="n">
         <v>0</v>
       </c>
-      <c r="AU316" t="inlineStr">
+      <c r="AU318" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV316" t="inlineStr">
+      <c r="AV318" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW316" t="inlineStr">
+      <c r="AW318" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX316" t="inlineStr">
+      <c r="AX318" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY316" t="inlineStr">
+      <c r="AY318" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ316" t="inlineStr">
+      <c r="AZ318" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA316" t="inlineStr">
+      <c r="BA318" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB316" t="inlineStr">
+      <c r="BB318" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC316" t="inlineStr">
+      <c r="BC318" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -57502,7 +57895,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -57512,7 +57905,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11">
@@ -57532,7 +57925,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">
@@ -57564,7 +57957,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32418</v>
+        <v>32431</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -53079,13 +53079,13 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R291" t="n">
-        <v>0.01101843545855937</v>
+        <v>0.01469124727807916</v>
       </c>
       <c r="S291" t="inlineStr">
         <is>
@@ -57124,12 +57124,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -57154,22 +57154,22 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N315" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O315" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R315" t="n">
-        <v>0</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -57202,42 +57202,42 @@
       </c>
       <c r="AV315" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57269,12 +57269,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -57308,95 +57308,81 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R316" t="n">
-        <v>0.03557618341728275</v>
+        <v>0</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AA316" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO316" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ316" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS316" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr"/>
       <c r="AT316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -57423,7 +57409,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -57467,103 +57453,28 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O317" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U317" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1340</t>
         </is>
       </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W317" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X317" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y317" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA317" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB317" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE317" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF317" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG317" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH317" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI317" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ317" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK317" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM317" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN317" t="b">
-        <v>1</v>
       </c>
       <c r="AO317" t="inlineStr">
         <is>
@@ -57657,123 +57568,357 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>3</v>
+      </c>
+      <c r="O318" t="n">
+        <v>3</v>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM318" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN318" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA318" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
+      <c r="F319" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
+      <c r="G319" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>D011</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
         <is>
           <t>戊型肝炎</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
+      <c r="K319" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
+      <c r="L319" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr">
+      <c r="M319" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N318" t="n">
-        <v>7</v>
-      </c>
-      <c r="O318" t="n">
-        <v>7</v>
-      </c>
-      <c r="R318" t="n">
-        <v>0.01356578946654432</v>
-      </c>
-      <c r="S318" t="inlineStr">
+      <c r="N319" t="n">
+        <v>9</v>
+      </c>
+      <c r="O319" t="n">
+        <v>9</v>
+      </c>
+      <c r="R319" t="n">
+        <v>0.01744172931412841</v>
+      </c>
+      <c r="S319" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO318" t="inlineStr">
+      <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP318" t="inlineStr">
+      <c r="AP319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR318" t="inlineStr">
+      <c r="AR319" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS318" t="inlineStr"/>
-      <c r="AT318" t="n">
+      <c r="AS319" t="inlineStr"/>
+      <c r="AT319" t="n">
         <v>0</v>
       </c>
-      <c r="AU318" t="inlineStr">
+      <c r="AU319" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV318" t="inlineStr">
+      <c r="AV319" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW318" t="inlineStr">
+      <c r="AW319" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX318" t="inlineStr">
+      <c r="AX319" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY318" t="inlineStr">
+      <c r="AY319" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ318" t="inlineStr">
+      <c r="AZ319" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA318" t="inlineStr">
+      <c r="BA319" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB318" t="inlineStr">
+      <c r="BB319" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC318" t="inlineStr">
+      <c r="BC319" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -57895,7 +58040,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -57905,7 +58050,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -57957,7 +58102,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32431</v>
+        <v>32446</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -50095,13 +50095,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O274" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R274" t="n">
-        <v>0.1802312029126603</v>
+        <v>0.1782932329888682</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32446</v>
+        <v>32445</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -54037,12 +54037,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -54076,13 +54076,16 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>8</v>
+        <v>2952</v>
       </c>
       <c r="O298" t="n">
-        <v>8</v>
+        <v>2952</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>0.142304733669131</v>
+        <v>0.2089299005528318</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
@@ -54091,7 +54094,7 @@
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -54101,7 +54104,7 @@
       </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP298" t="inlineStr">
@@ -54111,12 +54114,12 @@
       </c>
       <c r="AQ298" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS298" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT298" t="n">
@@ -54124,47 +54127,47 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -54196,12 +54199,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -54235,29 +54238,29 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>8</v>
+        <v>2952</v>
       </c>
       <c r="O299" t="n">
-        <v>8</v>
+        <v>2952</v>
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X299" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="Y299" t="inlineStr">
@@ -54267,7 +54270,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -54282,7 +54285,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -54297,7 +54300,7 @@
       </c>
       <c r="AF299" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG299" t="inlineStr">
@@ -54317,17 +54320,17 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+          <t>China CDC source-reported hepatitis E component.</t>
         </is>
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -54335,7 +54338,7 @@
       </c>
       <c r="AO299" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP299" t="inlineStr">
@@ -54345,12 +54348,12 @@
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT299" t="n">
@@ -54358,47 +54361,47 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA299" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB299" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC299" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -54430,12 +54433,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -54469,81 +54472,95 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="O300" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="R300" t="n">
-        <v>0.06976691725651366</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR300" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS300" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ300" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS300" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
       <c r="AT300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -54570,17 +54587,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -54614,22 +54631,39 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O301" t="n">
-        <v>6</v>
-      </c>
-      <c r="R301" t="n">
-        <v>0.05606928256970008</v>
-      </c>
-      <c r="S301" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -54637,6 +54671,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI301" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ301" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK301" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM301" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN301" t="b">
+        <v>1</v>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -54649,12 +54741,12 @@
       </c>
       <c r="AQ301" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS301" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+          <t>SER_FI_THL_TTR_1340</t>
         </is>
       </c>
       <c r="AT301" t="n">
@@ -54662,47 +54754,47 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -54729,17 +54821,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -54773,170 +54865,81 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="O302" t="n">
-        <v>6</v>
-      </c>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V302" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W302" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X302" t="inlineStr">
-        <is>
-          <t>Hepatit E</t>
-        </is>
-      </c>
-      <c r="Y302" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z302" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA302" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB302" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC302" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD302" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE302" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF302" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG302" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH302" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI302" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ302" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK302" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM302" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN302" t="b">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0.06976691725651366</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ302" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS302" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR302" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS302" t="inlineStr"/>
       <c r="AT302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -54968,12 +54971,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -54998,7 +55001,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -55007,81 +55010,95 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O303" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R303" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.05606928256970008</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR303" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS303" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ303" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS303" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -55108,17 +55125,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -55143,7 +55160,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -55152,26 +55169,103 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O304" t="n">
-        <v>0</v>
-      </c>
-      <c r="P304" t="n">
-        <v>0</v>
-      </c>
-      <c r="R304" t="n">
-        <v>0</v>
-      </c>
-      <c r="S304" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>6</v>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>Hepatit E</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF304" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG304" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH304" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI304" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ304" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK304" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM304" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN304" t="b">
+        <v>1</v>
       </c>
       <c r="AO304" t="inlineStr">
         <is>
@@ -55180,7 +55274,7 @@
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ304" t="inlineStr">
@@ -55190,55 +55284,55 @@
       </c>
       <c r="AS304" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -55265,17 +55359,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -55309,173 +55403,81 @@
         </is>
       </c>
       <c r="N305" t="n">
+        <v>13</v>
+      </c>
+      <c r="O305" t="n">
+        <v>13</v>
+      </c>
+      <c r="R305" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO305" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP305" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR305" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS305" t="inlineStr"/>
+      <c r="AT305" t="n">
         <v>0</v>
       </c>
-      <c r="O305" t="n">
-        <v>0</v>
-      </c>
-      <c r="P305" t="n">
-        <v>0</v>
-      </c>
-      <c r="U305" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V305" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W305" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X305" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y305" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z305" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA305" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB305" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC305" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD305" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE305" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF305" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG305" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH305" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI305" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ305" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK305" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM305" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN305" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO305" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP305" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ305" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS305" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT305" t="n">
-        <v>2</v>
-      </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA305" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55507,12 +55509,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -55537,7 +55539,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -55546,81 +55548,93 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O306" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="P306" t="n">
+        <v>0</v>
       </c>
       <c r="R306" t="n">
-        <v>0.007351275668091897</v>
+        <v>0</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP306" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR306" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS306" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ306" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS306" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV306" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -55647,7 +55661,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -55682,7 +55696,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -55691,26 +55705,106 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O307" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P307" t="n">
-        <v>3</v>
-      </c>
-      <c r="R307" t="n">
-        <v>0.05079797265291142</v>
-      </c>
-      <c r="S307" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC307" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF307" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ307" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK307" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM307" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN307" t="b">
+        <v>1</v>
       </c>
       <c r="AO307" t="inlineStr">
         <is>
@@ -55804,17 +55898,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -55848,173 +55942,81 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O308" t="n">
-        <v>3</v>
-      </c>
-      <c r="P308" t="n">
-        <v>3</v>
-      </c>
-      <c r="U308" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V308" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W308" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X308" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y308" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA308" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB308" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC308" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD308" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE308" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF308" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG308" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH308" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI308" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ308" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK308" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM308" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN308" t="b">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="R308" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO308" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP308" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ308" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS308" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR308" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS308" t="inlineStr"/>
       <c r="AT308" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV308" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA308" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB308" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC308" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56046,12 +56048,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -56076,7 +56078,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -56085,81 +56087,93 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O309" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="P309" t="n">
+        <v>3</v>
       </c>
       <c r="R309" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.05079797265291142</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP309" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR309" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS309" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ309" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS309" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56186,7 +56200,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -56221,7 +56235,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -56230,26 +56244,106 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O310" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P310" t="n">
-        <v>0</v>
-      </c>
-      <c r="R310" t="n">
-        <v>0</v>
-      </c>
-      <c r="S310" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE310" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF310" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG310" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH310" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI310" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ310" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK310" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM310" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN310" t="b">
+        <v>1</v>
       </c>
       <c r="AO310" t="inlineStr">
         <is>
@@ -56343,17 +56437,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -56387,173 +56481,81 @@
         </is>
       </c>
       <c r="N311" t="n">
+        <v>8</v>
+      </c>
+      <c r="O311" t="n">
+        <v>8</v>
+      </c>
+      <c r="R311" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO311" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP311" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR311" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS311" t="inlineStr"/>
+      <c r="AT311" t="n">
         <v>0</v>
       </c>
-      <c r="O311" t="n">
-        <v>0</v>
-      </c>
-      <c r="P311" t="n">
-        <v>0</v>
-      </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V311" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W311" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X311" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y311" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA311" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB311" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC311" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD311" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE311" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF311" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG311" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH311" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI311" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ311" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK311" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM311" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN311" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO311" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP311" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ311" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS311" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT311" t="n">
-        <v>2</v>
-      </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV311" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56585,12 +56587,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -56615,7 +56617,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -56624,81 +56626,93 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O312" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="P312" t="n">
+        <v>0</v>
       </c>
       <c r="R312" t="n">
-        <v>0.004900850445394598</v>
+        <v>0</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP312" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR312" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS312" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ312" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT312" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56725,7 +56739,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -56760,7 +56774,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -56769,26 +56783,106 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O313" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P313" t="n">
-        <v>4</v>
-      </c>
-      <c r="R313" t="n">
-        <v>0.0677306302038819</v>
-      </c>
-      <c r="S313" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ313" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK313" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM313" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN313" t="b">
+        <v>1</v>
       </c>
       <c r="AO313" t="inlineStr">
         <is>
@@ -56882,17 +56976,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -56926,173 +57020,81 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O314" t="n">
-        <v>4</v>
-      </c>
-      <c r="P314" t="n">
-        <v>4</v>
-      </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W314" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X314" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y314" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z314" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA314" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC314" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD314" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE314" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF314" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG314" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI314" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ314" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK314" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM314" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN314" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R314" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO314" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP314" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ314" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS314" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR314" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr"/>
       <c r="AT314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV314" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA314" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57124,12 +57126,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -57154,7 +57156,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -57163,81 +57165,93 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O315" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="P315" t="n">
+        <v>4</v>
       </c>
       <c r="R315" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.0677306302038819</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP315" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR315" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS315" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV315" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57264,17 +57278,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -57299,90 +57313,182 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N316" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O316" t="n">
-        <v>0</v>
-      </c>
-      <c r="R316" t="n">
-        <v>0</v>
-      </c>
-      <c r="S316" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P316" t="n">
+        <v>4</v>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ316" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK316" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM316" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN316" t="b">
+        <v>1</v>
       </c>
       <c r="AO316" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR316" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS316" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57414,12 +57520,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -57444,104 +57550,90 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N317" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O317" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="R317" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AA317" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO317" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ317" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS317" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr"/>
       <c r="AT317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV317" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA317" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB317" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC317" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57568,17 +57660,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -57603,112 +57695,35 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O318" t="n">
-        <v>3</v>
-      </c>
-      <c r="U318" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="V318" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W318" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X318" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y318" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z318" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>1</v>
+      </c>
+      <c r="P318" t="n">
+        <v>1</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB318" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC318" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD318" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE318" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF318" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG318" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH318" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI318" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ318" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK318" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM318" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN318" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO318" t="inlineStr">
         <is>
@@ -57717,65 +57732,65 @@
       </c>
       <c r="AP318" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ318" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS318" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA318" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB318" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC318" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57802,123 +57817,898 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>1</v>
+      </c>
+      <c r="O319" t="n">
+        <v>1</v>
+      </c>
+      <c r="P319" t="n">
+        <v>1</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN319" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>0</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0</v>
+      </c>
+      <c r="R320" t="n">
+        <v>0</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP320" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR320" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr"/>
+      <c r="AT320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV320" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW320" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA320" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB320" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC320" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>3</v>
+      </c>
+      <c r="O321" t="n">
+        <v>3</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ321" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV321" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA321" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC321" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>3</v>
+      </c>
+      <c r="O322" t="n">
+        <v>3</v>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI322" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ322" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK322" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM322" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN322" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO322" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP322" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ322" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT322" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV322" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW322" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA322" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB322" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC322" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
+      <c r="G323" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>D011</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
         <is>
           <t>戊型肝炎</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
+      <c r="K323" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
+      <c r="L323" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr">
+      <c r="M323" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N319" t="n">
+      <c r="N323" t="n">
         <v>9</v>
       </c>
-      <c r="O319" t="n">
+      <c r="O323" t="n">
         <v>9</v>
       </c>
-      <c r="R319" t="n">
+      <c r="R323" t="n">
         <v>0.01744172931412841</v>
       </c>
-      <c r="S319" t="inlineStr">
+      <c r="S323" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO319" t="inlineStr">
+      <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP319" t="inlineStr">
+      <c r="AP323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR319" t="inlineStr">
+      <c r="AR323" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS319" t="inlineStr"/>
-      <c r="AT319" t="n">
+      <c r="AS323" t="inlineStr"/>
+      <c r="AT323" t="n">
         <v>0</v>
       </c>
-      <c r="AU319" t="inlineStr">
+      <c r="AU323" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV319" t="inlineStr">
+      <c r="AV323" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW319" t="inlineStr">
+      <c r="AW323" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX319" t="inlineStr">
+      <c r="AX323" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY319" t="inlineStr">
+      <c r="AY323" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ319" t="inlineStr">
+      <c r="AZ323" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA319" t="inlineStr">
+      <c r="BA323" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB319" t="inlineStr">
+      <c r="BB323" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC319" t="inlineStr">
+      <c r="BC323" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -58040,7 +58830,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
@@ -58050,7 +58840,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
@@ -58070,7 +58860,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
@@ -58102,7 +58892,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32445</v>
+        <v>35398</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -45936,13 +45936,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O252" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R252" t="n">
-        <v>0.06660895370877544</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -54037,12 +54037,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -54076,98 +54076,81 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>2952</v>
+        <v>8</v>
       </c>
       <c r="O298" t="n">
-        <v>2952</v>
-      </c>
-      <c r="Q298" t="n">
+        <v>8</v>
+      </c>
+      <c r="R298" t="n">
+        <v>0.08881193827836725</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO298" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP298" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR298" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr"/>
+      <c r="AT298" t="n">
         <v>0</v>
       </c>
-      <c r="R298" t="n">
-        <v>0.2089299005528318</v>
-      </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AA298" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO298" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP298" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ298" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS298" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT298" t="n">
-        <v>1</v>
-      </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -54194,7 +54177,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -54243,98 +54226,26 @@
       <c r="O299" t="n">
         <v>2952</v>
       </c>
+      <c r="Q299" t="n">
+        <v>0</v>
+      </c>
+      <c r="R299" t="n">
+        <v>0.2089299005528318</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U299" t="inlineStr">
         <is>
           <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>SER_CN_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W299" t="inlineStr">
-        <is>
-          <t>SRC_CN_CDC</t>
-        </is>
-      </c>
-      <c r="X299" t="inlineStr">
-        <is>
-          <t>戊型肝炎</t>
-        </is>
-      </c>
-      <c r="Y299" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB299" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>country:CN:national</t>
-        </is>
-      </c>
-      <c r="AD299" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE299" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF299" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG299" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH299" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI299" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ299" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK299" t="inlineStr">
-        <is>
-          <t>China CDC source-reported hepatitis E component.</t>
-        </is>
-      </c>
-      <c r="AM299" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN299" t="b">
-        <v>1</v>
       </c>
       <c r="AO299" t="inlineStr">
         <is>
@@ -54428,17 +54339,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -54472,22 +54383,39 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>8</v>
+        <v>2952</v>
       </c>
       <c r="O300" t="n">
-        <v>8</v>
-      </c>
-      <c r="R300" t="n">
-        <v>0.142304733669131</v>
-      </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2952</v>
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>SRC_CN_CDC</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -54495,9 +54423,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>country:CN:national</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ300" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK300" t="inlineStr">
+        <is>
+          <t>China CDC source-reported hepatitis E component.</t>
+        </is>
+      </c>
+      <c r="AM300" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN300" t="b">
+        <v>1</v>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
@@ -54507,12 +54493,12 @@
       </c>
       <c r="AQ300" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT300" t="n">
@@ -54520,47 +54506,47 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -54587,7 +54573,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -54636,98 +54622,23 @@
       <c r="O301" t="n">
         <v>8</v>
       </c>
+      <c r="R301" t="n">
+        <v>0.142304733669131</v>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U301" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1340</t>
         </is>
       </c>
-      <c r="V301" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W301" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X301" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y301" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z301" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA301" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB301" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD301" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE301" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF301" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG301" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH301" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI301" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ301" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK301" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM301" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN301" t="b">
-        <v>1</v>
       </c>
       <c r="AO301" t="inlineStr">
         <is>
@@ -54821,17 +54732,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -54865,81 +54776,170 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="O302" t="n">
-        <v>36</v>
-      </c>
-      <c r="R302" t="n">
-        <v>0.06976691725651366</v>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ302" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK302" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM302" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN302" t="b">
+        <v>1</v>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR302" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS302" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ302" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS302" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
       <c r="AT302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -54971,12 +54971,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -55010,95 +55010,81 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="O303" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="R303" t="n">
-        <v>0.05606928256970008</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AA303" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO303" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ303" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS303" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR303" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS303" t="inlineStr"/>
       <c r="AT303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -55125,7 +55111,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -55174,98 +55160,23 @@
       <c r="O304" t="n">
         <v>6</v>
       </c>
+      <c r="R304" t="n">
+        <v>0.05606928256970008</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U304" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
         </is>
       </c>
-      <c r="V304" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W304" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X304" t="inlineStr">
-        <is>
-          <t>Hepatit E</t>
-        </is>
-      </c>
-      <c r="Y304" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z304" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA304" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB304" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC304" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD304" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE304" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF304" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG304" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH304" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI304" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ304" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK304" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM304" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN304" t="b">
-        <v>1</v>
       </c>
       <c r="AO304" t="inlineStr">
         <is>
@@ -55359,17 +55270,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -55394,7 +55305,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -55403,81 +55314,170 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O305" t="n">
-        <v>13</v>
-      </c>
-      <c r="R305" t="n">
-        <v>0.01061850929835496</v>
-      </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>Hepatit E</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ305" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK305" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM305" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN305" t="b">
+        <v>1</v>
       </c>
       <c r="AO305" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP305" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR305" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS305" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ305" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS305" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA305" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -55509,12 +55509,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -55548,93 +55548,81 @@
         </is>
       </c>
       <c r="N306" t="n">
+        <v>13</v>
+      </c>
+      <c r="O306" t="n">
+        <v>13</v>
+      </c>
+      <c r="R306" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO306" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP306" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR306" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS306" t="inlineStr"/>
+      <c r="AT306" t="n">
         <v>0</v>
       </c>
-      <c r="O306" t="n">
-        <v>0</v>
-      </c>
-      <c r="P306" t="n">
-        <v>0</v>
-      </c>
-      <c r="R306" t="n">
-        <v>0</v>
-      </c>
-      <c r="S306" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA306" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO306" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP306" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ306" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS306" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT306" t="n">
-        <v>2</v>
-      </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV306" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55661,7 +55649,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -55713,98 +55701,18 @@
       <c r="P307" t="n">
         <v>0</v>
       </c>
-      <c r="U307" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V307" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W307" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X307" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y307" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z307" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R307" t="n">
+        <v>0</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB307" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC307" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD307" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE307" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF307" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG307" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH307" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI307" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ307" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK307" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM307" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN307" t="b">
-        <v>1</v>
       </c>
       <c r="AO307" t="inlineStr">
         <is>
@@ -55898,17 +55806,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -55933,7 +55841,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -55942,81 +55850,173 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O308" t="n">
-        <v>9</v>
-      </c>
-      <c r="R308" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S308" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P308" t="n">
+        <v>0</v>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB308" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC308" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF308" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG308" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH308" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI308" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ308" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK308" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM308" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN308" t="b">
+        <v>1</v>
       </c>
       <c r="AO308" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP308" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR308" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS308" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ308" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS308" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV308" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA308" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB308" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC308" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56048,12 +56048,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -56087,93 +56087,81 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O309" t="n">
-        <v>3</v>
-      </c>
-      <c r="P309" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R309" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA309" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO309" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP309" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ309" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS309" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR309" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS309" t="inlineStr"/>
       <c r="AT309" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56200,7 +56188,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -56252,98 +56240,18 @@
       <c r="P310" t="n">
         <v>3</v>
       </c>
-      <c r="U310" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V310" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W310" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X310" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y310" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R310" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB310" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC310" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD310" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE310" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF310" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG310" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH310" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI310" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ310" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK310" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM310" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN310" t="b">
-        <v>1</v>
       </c>
       <c r="AO310" t="inlineStr">
         <is>
@@ -56437,17 +56345,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -56472,7 +56380,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -56481,81 +56389,173 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O311" t="n">
-        <v>8</v>
-      </c>
-      <c r="R311" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S311" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P311" t="n">
+        <v>3</v>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ311" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK311" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM311" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN311" t="b">
+        <v>1</v>
       </c>
       <c r="AO311" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP311" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR311" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS311" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ311" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS311" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT311" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV311" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56587,12 +56587,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -56626,93 +56626,81 @@
         </is>
       </c>
       <c r="N312" t="n">
+        <v>8</v>
+      </c>
+      <c r="O312" t="n">
+        <v>8</v>
+      </c>
+      <c r="R312" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO312" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP312" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR312" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr"/>
+      <c r="AT312" t="n">
         <v>0</v>
       </c>
-      <c r="O312" t="n">
-        <v>0</v>
-      </c>
-      <c r="P312" t="n">
-        <v>0</v>
-      </c>
-      <c r="R312" t="n">
-        <v>0</v>
-      </c>
-      <c r="S312" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA312" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO312" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP312" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ312" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS312" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT312" t="n">
-        <v>2</v>
-      </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56739,7 +56727,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -56791,98 +56779,18 @@
       <c r="P313" t="n">
         <v>0</v>
       </c>
-      <c r="U313" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V313" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W313" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X313" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y313" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z313" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R313" t="n">
+        <v>0</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB313" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC313" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD313" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE313" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF313" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG313" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH313" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI313" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ313" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK313" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM313" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN313" t="b">
-        <v>1</v>
       </c>
       <c r="AO313" t="inlineStr">
         <is>
@@ -56976,17 +56884,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -57011,7 +56919,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -57020,81 +56928,173 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O314" t="n">
-        <v>6</v>
-      </c>
-      <c r="R314" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P314" t="n">
+        <v>0</v>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ314" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK314" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM314" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN314" t="b">
+        <v>1</v>
       </c>
       <c r="AO314" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP314" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR314" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS314" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV314" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA314" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57126,12 +57126,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -57165,93 +57165,81 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O315" t="n">
-        <v>4</v>
-      </c>
-      <c r="P315" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R315" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA315" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO315" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP315" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ315" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS315" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr"/>
       <c r="AT315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV315" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57278,7 +57266,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -57330,98 +57318,18 @@
       <c r="P316" t="n">
         <v>4</v>
       </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W316" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X316" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y316" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z316" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R316" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB316" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD316" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE316" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF316" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG316" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH316" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI316" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ316" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK316" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM316" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN316" t="b">
-        <v>1</v>
       </c>
       <c r="AO316" t="inlineStr">
         <is>
@@ -57515,17 +57423,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -57550,7 +57458,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -57559,81 +57467,173 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O317" t="n">
-        <v>11</v>
-      </c>
-      <c r="R317" t="n">
-        <v>0.00898489248322343</v>
-      </c>
-      <c r="S317" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P317" t="n">
+        <v>4</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN317" t="b">
+        <v>1</v>
       </c>
       <c r="AO317" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR317" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS317" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV317" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA317" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB317" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC317" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57665,12 +57665,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -57704,93 +57704,81 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O318" t="n">
-        <v>1</v>
-      </c>
-      <c r="P318" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R318" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA318" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO318" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP318" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ318" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS318" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr"/>
       <c r="AT318" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA318" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB318" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC318" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57817,7 +57805,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -57869,98 +57857,18 @@
       <c r="P319" t="n">
         <v>1</v>
       </c>
-      <c r="U319" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W319" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X319" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y319" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R319" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC319" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD319" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE319" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF319" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG319" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI319" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ319" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK319" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM319" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN319" t="b">
-        <v>1</v>
       </c>
       <c r="AO319" t="inlineStr">
         <is>
@@ -58054,17 +57962,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -58089,90 +57997,182 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O320" t="n">
-        <v>0</v>
-      </c>
-      <c r="R320" t="n">
-        <v>0</v>
-      </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P320" t="n">
+        <v>1</v>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ320" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK320" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM320" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN320" t="b">
+        <v>1</v>
       </c>
       <c r="AO320" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP320" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR320" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS320" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT320" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV320" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ320" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA320" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB320" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC320" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58204,12 +58204,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -58243,95 +58243,81 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O321" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R321" t="n">
-        <v>0.05336427512592412</v>
+        <v>0</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AA321" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO321" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP321" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ321" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS321" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr"/>
       <c r="AT321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV321" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ321" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA321" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB321" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC321" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -58358,7 +58344,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -58407,98 +58393,23 @@
       <c r="O322" t="n">
         <v>3</v>
       </c>
+      <c r="R322" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U322" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1340</t>
         </is>
       </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W322" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X322" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y322" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD322" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE322" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF322" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG322" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH322" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI322" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ322" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK322" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM322" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN322" t="b">
-        <v>1</v>
       </c>
       <c r="AO322" t="inlineStr">
         <is>
@@ -58592,123 +58503,357 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N323" t="n">
+        <v>3</v>
+      </c>
+      <c r="O323" t="n">
+        <v>3</v>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ323" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK323" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM323" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN323" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO323" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP323" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT323" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV323" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW323" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX323" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY323" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA323" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB323" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC323" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
+      <c r="F324" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
+      <c r="G324" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>D011</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
         <is>
           <t>戊型肝炎</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
+      <c r="K324" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
+      <c r="L324" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr">
+      <c r="M324" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N323" t="n">
+      <c r="N324" t="n">
         <v>9</v>
       </c>
-      <c r="O323" t="n">
+      <c r="O324" t="n">
         <v>9</v>
       </c>
-      <c r="R323" t="n">
+      <c r="R324" t="n">
         <v>0.01744172931412841</v>
       </c>
-      <c r="S323" t="inlineStr">
+      <c r="S324" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO323" t="inlineStr">
+      <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP323" t="inlineStr">
+      <c r="AP324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR323" t="inlineStr">
+      <c r="AR324" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS323" t="inlineStr"/>
-      <c r="AT323" t="n">
+      <c r="AS324" t="inlineStr"/>
+      <c r="AT324" t="n">
         <v>0</v>
       </c>
-      <c r="AU323" t="inlineStr">
+      <c r="AU324" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV323" t="inlineStr">
+      <c r="AV324" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW323" t="inlineStr">
+      <c r="AW324" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX323" t="inlineStr">
+      <c r="AX324" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY323" t="inlineStr">
+      <c r="AY324" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ323" t="inlineStr">
+      <c r="AZ324" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA323" t="inlineStr">
+      <c r="BA324" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB323" t="inlineStr">
+      <c r="BB324" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC323" t="inlineStr">
+      <c r="BC324" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -58830,7 +58975,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -58840,7 +58985,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
@@ -58892,7 +59037,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35398</v>
+        <v>35407</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -58781,13 +58781,13 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O324" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R324" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
@@ -59037,7 +59037,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35407</v>
+        <v>35408</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -50095,13 +50095,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O274" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R274" t="n">
-        <v>0.1782932329888682</v>
+        <v>0.1802312029126603</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -58388,13 +58388,13 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O322" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R322" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S322" t="inlineStr">
         <is>
@@ -58547,10 +58547,10 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
@@ -58781,13 +58781,13 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O324" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R324" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
@@ -58856,6 +58856,151 @@
       <c r="BC324" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>6</v>
+      </c>
+      <c r="O325" t="n">
+        <v>6</v>
+      </c>
+      <c r="R325" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO325" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP325" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR325" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr"/>
+      <c r="AT325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU325" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV325" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW325" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX325" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY325" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA325" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB325" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC325" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58892,7 +59037,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -58975,7 +59120,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -58985,7 +59130,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -59037,7 +59182,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35408</v>
+        <v>35420</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -58781,13 +58781,13 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O324" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R324" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
@@ -59182,7 +59182,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35420</v>
+        <v>35422</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -58781,13 +58781,13 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O324" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R324" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03875939847584092</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
@@ -59001,6 +59001,400 @@
       <c r="BC325" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>2</v>
+      </c>
+      <c r="O326" t="n">
+        <v>2</v>
+      </c>
+      <c r="P326" t="n">
+        <v>2</v>
+      </c>
+      <c r="R326" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO326" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP326" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ326" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU326" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV326" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW326" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX326" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY326" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA326" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB326" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC326" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>2</v>
+      </c>
+      <c r="O327" t="n">
+        <v>2</v>
+      </c>
+      <c r="P327" t="n">
+        <v>2</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM327" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN327" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO327" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP327" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ327" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT327" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU327" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV327" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW327" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX327" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY327" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA327" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB327" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC327" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -59120,7 +59514,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -59130,7 +59524,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11">
@@ -59150,7 +59544,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
@@ -59182,7 +59576,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35422</v>
+        <v>35428</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -58781,13 +58781,13 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="O324" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="R324" t="n">
-        <v>0.03875939847584092</v>
+        <v>0.05232518794238524</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
@@ -59576,7 +59576,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35428</v>
+        <v>35435</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -46325,7 +46325,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -54465,7 +54465,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -54971,12 +54971,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -55010,13 +55010,13 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="O303" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="R303" t="n">
-        <v>0.06976691725651366</v>
+        <v>0.1219743252177038</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
@@ -55049,42 +55049,42 @@
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -55116,12 +55116,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -55155,95 +55155,81 @@
         </is>
       </c>
       <c r="N304" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="O304" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="R304" t="n">
-        <v>0.05606928256970008</v>
+        <v>0.06589097740892956</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AA304" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO304" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ304" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS304" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR304" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS304" t="inlineStr"/>
       <c r="AT304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -55270,7 +55256,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -55319,98 +55305,23 @@
       <c r="O305" t="n">
         <v>6</v>
       </c>
+      <c r="R305" t="n">
+        <v>0.05606928256970008</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U305" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
         </is>
       </c>
-      <c r="V305" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W305" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X305" t="inlineStr">
-        <is>
-          <t>Hepatit E</t>
-        </is>
-      </c>
-      <c r="Y305" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z305" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA305" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB305" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC305" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD305" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE305" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF305" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG305" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH305" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI305" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ305" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK305" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM305" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN305" t="b">
-        <v>1</v>
       </c>
       <c r="AO305" t="inlineStr">
         <is>
@@ -55504,17 +55415,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -55539,7 +55450,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -55548,81 +55459,170 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O306" t="n">
-        <v>13</v>
-      </c>
-      <c r="R306" t="n">
-        <v>0.01061850929835496</v>
-      </c>
-      <c r="S306" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>Hepatit E</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD306" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF306" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG306" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ306" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK306" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM306" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN306" t="b">
+        <v>1</v>
       </c>
       <c r="AO306" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP306" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR306" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS306" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ306" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS306" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV306" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -55654,12 +55654,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -55693,93 +55693,81 @@
         </is>
       </c>
       <c r="N307" t="n">
+        <v>13</v>
+      </c>
+      <c r="O307" t="n">
+        <v>13</v>
+      </c>
+      <c r="R307" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO307" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP307" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR307" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS307" t="inlineStr"/>
+      <c r="AT307" t="n">
         <v>0</v>
       </c>
-      <c r="O307" t="n">
-        <v>0</v>
-      </c>
-      <c r="P307" t="n">
-        <v>0</v>
-      </c>
-      <c r="R307" t="n">
-        <v>0</v>
-      </c>
-      <c r="S307" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA307" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO307" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP307" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ307" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS307" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT307" t="n">
-        <v>2</v>
-      </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV307" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA307" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB307" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC307" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55806,7 +55794,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -55858,98 +55846,18 @@
       <c r="P308" t="n">
         <v>0</v>
       </c>
-      <c r="U308" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V308" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W308" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X308" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y308" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R308" t="n">
+        <v>0</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB308" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC308" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD308" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE308" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF308" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG308" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH308" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI308" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ308" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK308" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM308" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN308" t="b">
-        <v>1</v>
       </c>
       <c r="AO308" t="inlineStr">
         <is>
@@ -56043,17 +55951,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -56078,7 +55986,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -56087,81 +55995,173 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O309" t="n">
-        <v>9</v>
-      </c>
-      <c r="R309" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S309" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P309" t="n">
+        <v>0</v>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ309" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK309" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM309" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN309" t="b">
+        <v>1</v>
       </c>
       <c r="AO309" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP309" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR309" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS309" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ309" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS309" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56193,12 +56193,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -56232,93 +56232,81 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O310" t="n">
-        <v>3</v>
-      </c>
-      <c r="P310" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R310" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA310" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO310" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP310" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ310" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS310" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR310" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS310" t="inlineStr"/>
       <c r="AT310" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV310" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA310" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB310" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC310" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56345,7 +56333,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -56397,98 +56385,18 @@
       <c r="P311" t="n">
         <v>3</v>
       </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V311" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W311" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X311" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y311" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R311" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB311" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC311" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD311" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE311" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF311" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG311" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH311" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI311" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ311" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK311" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM311" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN311" t="b">
-        <v>1</v>
       </c>
       <c r="AO311" t="inlineStr">
         <is>
@@ -56582,17 +56490,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -56617,7 +56525,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -56626,81 +56534,173 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O312" t="n">
-        <v>8</v>
-      </c>
-      <c r="R312" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S312" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P312" t="n">
+        <v>3</v>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB312" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF312" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI312" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ312" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK312" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM312" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN312" t="b">
+        <v>1</v>
       </c>
       <c r="AO312" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP312" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR312" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS312" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ312" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT312" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56732,12 +56732,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -56771,93 +56771,81 @@
         </is>
       </c>
       <c r="N313" t="n">
+        <v>8</v>
+      </c>
+      <c r="O313" t="n">
+        <v>8</v>
+      </c>
+      <c r="R313" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO313" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP313" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR313" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr"/>
+      <c r="AT313" t="n">
         <v>0</v>
       </c>
-      <c r="O313" t="n">
-        <v>0</v>
-      </c>
-      <c r="P313" t="n">
-        <v>0</v>
-      </c>
-      <c r="R313" t="n">
-        <v>0</v>
-      </c>
-      <c r="S313" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA313" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO313" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP313" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ313" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS313" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT313" t="n">
-        <v>2</v>
-      </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV313" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA313" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB313" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC313" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56884,7 +56872,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -56936,98 +56924,18 @@
       <c r="P314" t="n">
         <v>0</v>
       </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W314" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X314" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y314" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z314" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R314" t="n">
+        <v>0</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC314" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD314" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE314" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF314" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG314" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI314" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ314" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK314" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM314" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN314" t="b">
-        <v>1</v>
       </c>
       <c r="AO314" t="inlineStr">
         <is>
@@ -57121,17 +57029,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -57156,7 +57064,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -57165,81 +57073,173 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O315" t="n">
-        <v>6</v>
-      </c>
-      <c r="R315" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S315" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P315" t="n">
+        <v>0</v>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN315" t="b">
+        <v>1</v>
       </c>
       <c r="AO315" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP315" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR315" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS315" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV315" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57271,12 +57271,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -57310,93 +57310,81 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O316" t="n">
-        <v>4</v>
-      </c>
-      <c r="P316" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R316" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA316" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO316" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ316" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS316" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr"/>
       <c r="AT316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57423,7 +57411,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -57475,98 +57463,18 @@
       <c r="P317" t="n">
         <v>4</v>
       </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W317" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X317" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y317" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R317" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB317" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE317" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF317" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG317" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH317" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI317" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ317" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK317" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM317" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN317" t="b">
-        <v>1</v>
       </c>
       <c r="AO317" t="inlineStr">
         <is>
@@ -57660,17 +57568,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -57695,7 +57603,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -57704,81 +57612,173 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O318" t="n">
-        <v>11</v>
-      </c>
-      <c r="R318" t="n">
-        <v>0.00898489248322343</v>
-      </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P318" t="n">
+        <v>4</v>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM318" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN318" t="b">
+        <v>1</v>
       </c>
       <c r="AO318" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP318" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR318" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS318" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA318" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB318" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC318" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57810,12 +57810,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -57849,93 +57849,81 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O319" t="n">
-        <v>1</v>
-      </c>
-      <c r="P319" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R319" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA319" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO319" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP319" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ319" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS319" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr"/>
       <c r="AT319" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV319" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ319" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA319" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB319" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC319" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57962,7 +57950,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -58014,98 +58002,18 @@
       <c r="P320" t="n">
         <v>1</v>
       </c>
-      <c r="U320" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V320" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W320" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X320" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y320" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z320" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R320" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC320" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD320" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE320" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF320" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG320" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH320" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI320" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ320" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK320" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM320" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN320" t="b">
-        <v>1</v>
       </c>
       <c r="AO320" t="inlineStr">
         <is>
@@ -58199,17 +58107,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -58234,90 +58142,182 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O321" t="n">
-        <v>0</v>
-      </c>
-      <c r="R321" t="n">
-        <v>0</v>
-      </c>
-      <c r="S321" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P321" t="n">
+        <v>1</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN321" t="b">
+        <v>1</v>
       </c>
       <c r="AO321" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP321" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR321" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS321" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ321" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT321" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV321" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ321" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA321" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB321" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC321" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58349,12 +58349,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -58388,95 +58388,81 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O322" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R322" t="n">
-        <v>0.07115236683456549</v>
+        <v>0</v>
       </c>
       <c r="S322" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AA322" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO322" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP322" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ322" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS322" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr"/>
       <c r="AT322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV322" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA322" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB322" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC322" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -58503,7 +58489,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -58547,103 +58533,28 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O323" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="R323" t="n">
+        <v>0.1600928253777724</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U323" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1340</t>
         </is>
       </c>
-      <c r="V323" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W323" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X323" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y323" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z323" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA323" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB323" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC323" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD323" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE323" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF323" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG323" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH323" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI323" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ323" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK323" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM323" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN323" t="b">
-        <v>1</v>
       </c>
       <c r="AO323" t="inlineStr">
         <is>
@@ -58737,17 +58648,17 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -58781,81 +58692,170 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="O324" t="n">
-        <v>27</v>
-      </c>
-      <c r="R324" t="n">
-        <v>0.05232518794238524</v>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM324" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN324" t="b">
+        <v>1</v>
       </c>
       <c r="AO324" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP324" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR324" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS324" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ324" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
       <c r="AT324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV324" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA324" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB324" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC324" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -58887,12 +58887,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -58917,7 +58917,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -58926,13 +58926,13 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="O325" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="R325" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.05426315786617728</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
@@ -58965,42 +58965,42 @@
       </c>
       <c r="AV325" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA325" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB325" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC325" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -59032,12 +59032,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -59071,93 +59071,81 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O326" t="n">
-        <v>2</v>
-      </c>
-      <c r="P326" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R326" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA326" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO326" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP326" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ326" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS326" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR326" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr"/>
       <c r="AT326" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV326" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ326" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA326" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB326" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC326" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -59184,7 +59172,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -59236,98 +59224,18 @@
       <c r="P327" t="n">
         <v>2</v>
       </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V327" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W327" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X327" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y327" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z327" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R327" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB327" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC327" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD327" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE327" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF327" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG327" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI327" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ327" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK327" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM327" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN327" t="b">
-        <v>1</v>
       </c>
       <c r="AO327" t="inlineStr">
         <is>
@@ -59393,6 +59301,782 @@
         </is>
       </c>
       <c r="BC327" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>2</v>
+      </c>
+      <c r="O328" t="n">
+        <v>2</v>
+      </c>
+      <c r="P328" t="n">
+        <v>2</v>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF328" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ328" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK328" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM328" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN328" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO328" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP328" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ328" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS328" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU328" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV328" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW328" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX328" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY328" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA328" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB328" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC328" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>5</v>
+      </c>
+      <c r="O329" t="n">
+        <v>5</v>
+      </c>
+      <c r="R329" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO329" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP329" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR329" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS329" t="inlineStr"/>
+      <c r="AT329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU329" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV329" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW329" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX329" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY329" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA329" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB329" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC329" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N330" t="n">
+        <v>5</v>
+      </c>
+      <c r="O330" t="n">
+        <v>5</v>
+      </c>
+      <c r="P330" t="n">
+        <v>5</v>
+      </c>
+      <c r="R330" t="n">
+        <v>0.08466328775485238</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO330" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP330" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ330" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS330" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU330" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV330" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW330" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX330" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY330" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA330" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB330" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC330" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>5</v>
+      </c>
+      <c r="O331" t="n">
+        <v>5</v>
+      </c>
+      <c r="P331" t="n">
+        <v>5</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK331" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM331" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN331" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO331" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP331" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ331" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS331" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT331" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU331" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV331" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW331" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX331" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY331" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA331" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB331" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC331" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -59431,7 +60115,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -59514,7 +60198,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
@@ -59524,7 +60208,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11">
@@ -59544,7 +60228,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13">
@@ -59576,7 +60260,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35435</v>
+        <v>35458</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -58235,13 +58235,13 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O320" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R320" t="n">
-        <v>0.06589097740892956</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S320" t="inlineStr">
         <is>
@@ -62006,13 +62006,13 @@
         </is>
       </c>
       <c r="N341" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O341" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R341" t="n">
-        <v>0.05426315786617728</v>
+        <v>0.06201503756134547</v>
       </c>
       <c r="S341" t="inlineStr">
         <is>
@@ -62835,16 +62835,16 @@
         </is>
       </c>
       <c r="N346" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O346" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P346" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R346" t="n">
-        <v>0.08466328775485238</v>
+        <v>0.0677306302038819</v>
       </c>
       <c r="S346" t="inlineStr">
         <is>
@@ -62992,13 +62992,13 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O347" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P347" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U347" t="inlineStr">
         <is>
@@ -63159,6 +63159,1083 @@
       <c r="BC347" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N348" t="n">
+        <v>6</v>
+      </c>
+      <c r="O348" t="n">
+        <v>6</v>
+      </c>
+      <c r="R348" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO348" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP348" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR348" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS348" t="inlineStr"/>
+      <c r="AT348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU348" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV348" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW348" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX348" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY348" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA348" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB348" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC348" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N349" t="n">
+        <v>1</v>
+      </c>
+      <c r="O349" t="n">
+        <v>1</v>
+      </c>
+      <c r="P349" t="n">
+        <v>1</v>
+      </c>
+      <c r="R349" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO349" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP349" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ349" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS349" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT349" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU349" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV349" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW349" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX349" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY349" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA349" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB349" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC349" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N350" t="n">
+        <v>1</v>
+      </c>
+      <c r="O350" t="n">
+        <v>1</v>
+      </c>
+      <c r="P350" t="n">
+        <v>1</v>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB350" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE350" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF350" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI350" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ350" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK350" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM350" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN350" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO350" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP350" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ350" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT350" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU350" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV350" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW350" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX350" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY350" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA350" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB350" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC350" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N351" t="n">
+        <v>0</v>
+      </c>
+      <c r="O351" t="n">
+        <v>0</v>
+      </c>
+      <c r="R351" t="n">
+        <v>0</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO351" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP351" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ351" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS351" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU351" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV351" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW351" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX351" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY351" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA351" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB351" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC351" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N352" t="n">
+        <v>0</v>
+      </c>
+      <c r="O352" t="n">
+        <v>0</v>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF352" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI352" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ352" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK352" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM352" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN352" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO352" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP352" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ352" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU352" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV352" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW352" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX352" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY352" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA352" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB352" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC352" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N353" t="n">
+        <v>0</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0</v>
+      </c>
+      <c r="R353" t="n">
+        <v>0</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO353" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP353" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR353" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS353" t="inlineStr"/>
+      <c r="AT353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU353" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV353" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW353" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX353" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY353" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA353" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB353" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC353" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -63195,7 +64272,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -63278,7 +64355,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
@@ -63288,7 +64365,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -63308,7 +64385,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -63340,7 +64417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36736</v>
+        <v>36748</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -71868,13 +71868,13 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O407" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R407" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S407" t="inlineStr">
         <is>
@@ -72124,7 +72124,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36755</v>
+        <v>36757</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1202,6 +1217,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1338,6 +1358,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1483,6 +1508,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1628,6 +1658,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1764,6 +1799,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1909,6 +1949,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2054,6 +2099,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6219,6 +6269,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6364,6 +6419,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9073,6 +9133,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9218,6 +9283,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9363,6 +9433,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9583,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9644,6 +9724,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9780,6 +9865,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9925,6 +10015,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10061,6 +10156,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10206,6 +10306,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10351,6 +10456,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14516,6 +14626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14661,6 +14776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15596,6 +15716,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17518,6 +17643,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17654,6 +17784,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17790,6 +17925,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17935,6 +18075,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18071,6 +18216,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18216,6 +18366,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18361,6 +18516,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18506,6 +18666,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18651,6 +18816,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18796,6 +18966,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22576,6 +22751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22721,6 +22901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23656,6 +23841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25969,6 +26159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26114,6 +26309,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26259,6 +26459,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26404,6 +26609,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26540,6 +26750,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26685,6 +26900,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26830,6 +27050,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26975,6 +27200,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27120,6 +27350,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27265,6 +27500,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31045,6 +31285,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31190,6 +31435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31728,6 +31978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34041,6 +34296,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34186,6 +34446,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34322,6 +34587,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34467,6 +34737,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34612,6 +34887,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34757,6 +35037,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34902,6 +35187,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35038,6 +35328,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35183,6 +35478,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35328,6 +35628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39493,6 +39798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39638,6 +39948,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42886,6 +43201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43031,6 +43351,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43167,6 +43492,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43312,6 +43642,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43457,6 +43792,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43602,6 +43942,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43747,6 +44092,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43892,6 +44242,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44037,6 +44392,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44182,6 +44542,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47962,6 +48327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48107,6 +48477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50801,6 +51176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50946,6 +51326,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51082,6 +51467,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51227,6 +51617,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51372,6 +51767,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51508,6 +51908,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51644,6 +52049,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51780,6 +52190,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51925,6 +52340,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52070,6 +52490,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56469,6 +56894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56614,6 +57044,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57152,6 +57587,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59598,6 +60038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO336" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59743,6 +60188,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59879,6 +60329,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60024,6 +60479,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60169,6 +60629,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60305,6 +60770,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60450,6 +60920,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60586,6 +61061,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60731,6 +61211,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60876,6 +61361,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64505,6 +64995,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64650,6 +65145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67883,6 +68383,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68028,6 +68533,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68173,6 +68683,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68318,6 +68833,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68463,6 +68983,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68608,6 +69133,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68753,6 +69283,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68898,6 +69433,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69043,6 +69583,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69568,17 +70113,22 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O394" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R394" t="n">
-        <v>0.06201503756134547</v>
+        <v>0.06395300748513752</v>
       </c>
       <c r="S394" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO394" t="inlineStr">
@@ -69674,12 +70224,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -69704,7 +70254,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
@@ -69713,81 +70263,95 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O395" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R395" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S395" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO395" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP395" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR395" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS395" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ395" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS395" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU395" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV395" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW395" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ395" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA395" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB395" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC395" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -69814,17 +70378,17 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -69849,7 +70413,7 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
@@ -69858,26 +70422,103 @@
         </is>
       </c>
       <c r="N396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O396" t="n">
-        <v>2</v>
-      </c>
-      <c r="P396" t="n">
-        <v>2</v>
-      </c>
-      <c r="R396" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S396" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>Hepatit E</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB396" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD396" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE396" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF396" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG396" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH396" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI396" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ396" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK396" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM396" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN396" t="b">
+        <v>1</v>
       </c>
       <c r="AO396" t="inlineStr">
         <is>
@@ -69886,7 +70527,7 @@
       </c>
       <c r="AP396" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ396" t="inlineStr">
@@ -69896,55 +70537,55 @@
       </c>
       <c r="AS396" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT396" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU396" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV396" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW396" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY396" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ396" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA396" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB396" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC396" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -69971,17 +70612,17 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -70015,173 +70656,81 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O397" t="n">
-        <v>2</v>
-      </c>
-      <c r="P397" t="n">
-        <v>2</v>
-      </c>
-      <c r="U397" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V397" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W397" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X397" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y397" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z397" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA397" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB397" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC397" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD397" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE397" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF397" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG397" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH397" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI397" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ397" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK397" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM397" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN397" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R397" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO397" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP397" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ397" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS397" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR397" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS397" t="inlineStr"/>
       <c r="AT397" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU397" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV397" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW397" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX397" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY397" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ397" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA397" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB397" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC397" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70213,12 +70762,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -70243,7 +70792,7 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -70252,81 +70801,93 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O398" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="P398" t="n">
+        <v>2</v>
       </c>
       <c r="R398" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO398" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP398" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR398" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS398" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ398" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS398" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT398" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU398" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV398" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW398" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX398" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY398" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ398" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA398" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB398" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC398" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -70353,7 +70914,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -70388,7 +70949,7 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
@@ -70397,26 +70958,106 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O399" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P399" t="n">
-        <v>4</v>
-      </c>
-      <c r="R399" t="n">
-        <v>0.0677306302038819</v>
-      </c>
-      <c r="S399" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA399" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB399" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC399" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD399" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE399" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF399" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG399" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH399" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI399" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ399" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK399" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM399" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN399" t="b">
+        <v>1</v>
       </c>
       <c r="AO399" t="inlineStr">
         <is>
@@ -70510,17 +71151,17 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -70554,173 +71195,81 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O400" t="n">
-        <v>4</v>
-      </c>
-      <c r="P400" t="n">
-        <v>4</v>
-      </c>
-      <c r="U400" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V400" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W400" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X400" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y400" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z400" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA400" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB400" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC400" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD400" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE400" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF400" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG400" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH400" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI400" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ400" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK400" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM400" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN400" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="R400" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO400" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP400" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ400" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS400" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR400" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS400" t="inlineStr"/>
       <c r="AT400" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU400" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV400" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW400" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ400" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA400" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB400" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC400" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70752,12 +71301,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -70782,7 +71331,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
@@ -70791,81 +71340,93 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O401" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="P401" t="n">
+        <v>4</v>
       </c>
       <c r="R401" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.0677306302038819</v>
       </c>
       <c r="S401" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO401" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP401" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR401" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS401" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ401" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS401" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT401" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU401" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV401" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW401" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX401" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY401" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ401" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA401" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB401" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC401" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -70892,7 +71453,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -70927,7 +71488,7 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
@@ -70936,26 +71497,106 @@
         </is>
       </c>
       <c r="N402" t="n">
+        <v>4</v>
+      </c>
+      <c r="O402" t="n">
+        <v>4</v>
+      </c>
+      <c r="P402" t="n">
+        <v>4</v>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB402" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC402" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD402" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE402" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF402" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG402" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH402" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI402" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ402" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK402" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM402" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN402" t="b">
         <v>1</v>
-      </c>
-      <c r="O402" t="n">
-        <v>1</v>
-      </c>
-      <c r="P402" t="n">
-        <v>1</v>
-      </c>
-      <c r="R402" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S402" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA402" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO402" t="inlineStr">
         <is>
@@ -71049,17 +71690,17 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -71093,173 +71734,81 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O403" t="n">
-        <v>1</v>
-      </c>
-      <c r="P403" t="n">
-        <v>1</v>
-      </c>
-      <c r="U403" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V403" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W403" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X403" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y403" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z403" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA403" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB403" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC403" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD403" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE403" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF403" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG403" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH403" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI403" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ403" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK403" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM403" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN403" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R403" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO403" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP403" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ403" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS403" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR403" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS403" t="inlineStr"/>
       <c r="AT403" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU403" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV403" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW403" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY403" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ403" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA403" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB403" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC403" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -71291,12 +71840,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -71321,7 +71870,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -71330,81 +71879,93 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O404" t="n">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="P404" t="n">
+        <v>1</v>
       </c>
       <c r="R404" t="n">
-        <v>0.005717658852960364</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO404" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP404" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR404" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS404" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ404" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS404" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU404" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV404" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW404" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ404" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA404" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB404" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC404" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -71431,17 +71992,17 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -71466,37 +72027,115 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O405" t="n">
-        <v>0</v>
-      </c>
-      <c r="R405" t="n">
-        <v>0</v>
-      </c>
-      <c r="S405" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P405" t="n">
+        <v>1</v>
       </c>
       <c r="U405" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y405" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA405" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB405" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC405" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD405" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE405" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF405" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG405" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH405" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI405" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ405" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK405" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM405" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN405" t="b">
+        <v>1</v>
       </c>
       <c r="AO405" t="inlineStr">
         <is>
@@ -71505,65 +72144,65 @@
       </c>
       <c r="AP405" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ405" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS405" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU405" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV405" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW405" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ405" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA405" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB405" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC405" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -71590,17 +72229,17 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -71625,179 +72264,90 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N406" t="n">
+        <v>7</v>
+      </c>
+      <c r="O406" t="n">
+        <v>7</v>
+      </c>
+      <c r="R406" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO406" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP406" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR406" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS406" t="inlineStr"/>
+      <c r="AT406" t="n">
         <v>0</v>
       </c>
-      <c r="O406" t="n">
-        <v>0</v>
-      </c>
-      <c r="U406" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="V406" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W406" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X406" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y406" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z406" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA406" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB406" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC406" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD406" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE406" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF406" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG406" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH406" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI406" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ406" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK406" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM406" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN406" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO406" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP406" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ406" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS406" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AT406" t="n">
-        <v>1</v>
-      </c>
       <c r="AU406" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV406" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW406" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ406" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA406" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB406" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC406" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -71829,118 +72379,910 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>5</v>
+      </c>
+      <c r="O407" t="n">
+        <v>5</v>
+      </c>
+      <c r="P407" t="n">
+        <v>5</v>
+      </c>
+      <c r="R407" t="n">
+        <v>0.08466328775485238</v>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO407" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP407" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ407" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS407" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT407" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU407" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV407" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW407" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX407" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY407" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA407" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB407" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC407" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>5</v>
+      </c>
+      <c r="O408" t="n">
+        <v>5</v>
+      </c>
+      <c r="P408" t="n">
+        <v>5</v>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB408" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC408" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD408" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE408" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF408" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG408" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH408" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI408" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ408" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK408" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM408" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN408" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO408" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP408" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ408" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS408" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT408" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU408" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV408" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW408" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX408" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY408" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA408" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB408" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC408" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>3</v>
+      </c>
+      <c r="O409" t="n">
+        <v>3</v>
+      </c>
+      <c r="R409" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO409" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP409" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ409" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS409" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT409" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU409" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV409" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW409" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX409" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY409" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA409" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB409" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC409" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>3</v>
+      </c>
+      <c r="O410" t="n">
+        <v>3</v>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X410" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y410" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z410" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB410" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC410" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD410" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE410" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF410" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG410" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH410" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI410" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ410" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK410" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM410" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN410" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO410" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP410" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ410" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS410" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AT410" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU410" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV410" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW410" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX410" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY410" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA410" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB410" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC410" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr">
+      <c r="G411" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>D011</t>
-        </is>
-      </c>
-      <c r="I407" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="J407" t="inlineStr">
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
         <is>
           <t>戊型肝炎</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr">
+      <c r="K411" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L407" t="inlineStr">
+      <c r="L411" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M407" t="inlineStr">
+      <c r="M411" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N407" t="n">
-        <v>2</v>
-      </c>
-      <c r="O407" t="n">
-        <v>2</v>
-      </c>
-      <c r="R407" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S407" t="inlineStr">
+      <c r="N411" t="n">
+        <v>3</v>
+      </c>
+      <c r="O411" t="n">
+        <v>3</v>
+      </c>
+      <c r="R411" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S411" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO407" t="inlineStr">
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO411" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP407" t="inlineStr">
+      <c r="AP411" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR407" t="inlineStr">
+      <c r="AR411" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS407" t="inlineStr"/>
-      <c r="AT407" t="n">
+      <c r="AS411" t="inlineStr"/>
+      <c r="AT411" t="n">
         <v>0</v>
       </c>
-      <c r="AU407" t="inlineStr">
+      <c r="AU411" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV407" t="inlineStr">
+      <c r="AV411" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW407" t="inlineStr">
+      <c r="AW411" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX407" t="inlineStr">
+      <c r="AX411" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY407" t="inlineStr">
+      <c r="AY411" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ407" t="inlineStr">
+      <c r="AZ411" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA407" t="inlineStr">
+      <c r="BA411" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB407" t="inlineStr">
+      <c r="BB411" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC407" t="inlineStr">
+      <c r="BC411" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -72062,7 +73404,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -72072,7 +73414,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11">
@@ -72092,7 +73434,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -72124,7 +73466,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36757</v>
+        <v>36770</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -70113,13 +70113,13 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O394" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R394" t="n">
-        <v>0.06395300748513752</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S394" t="inlineStr">
         <is>
@@ -73205,13 +73205,13 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O411" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="R411" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -73466,7 +73466,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36770</v>
+        <v>36781</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -65282,13 +65282,13 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O366" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R366" t="n">
-        <v>0.05606928256970008</v>
+        <v>0.04672440214141673</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
@@ -65441,10 +65441,10 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O367" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U367" t="inlineStr">
         <is>
@@ -72812,13 +72812,13 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O409" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R409" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S409" t="inlineStr">
         <is>
@@ -72971,10 +72971,10 @@
         </is>
       </c>
       <c r="N410" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O410" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U410" t="inlineStr">
         <is>
@@ -73285,6 +73285,151 @@
       <c r="BC411" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>7</v>
+      </c>
+      <c r="O412" t="n">
+        <v>7</v>
+      </c>
+      <c r="R412" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO412" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP412" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR412" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS412" t="inlineStr"/>
+      <c r="AT412" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU412" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV412" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW412" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX412" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY412" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA412" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB412" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC412" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -73321,7 +73466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -73404,7 +73549,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -73414,7 +73559,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11">
@@ -73466,7 +73611,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36781</v>
+        <v>36788</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -40085,13 +40085,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O224" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R224" t="n">
-        <v>0.05606928256970008</v>
+        <v>0.04672440214141673</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -40244,10 +40244,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O225" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -73611,7 +73611,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36788</v>
+        <v>36787</v>
       </c>
     </row>
     <row r="16">
